--- a/Conhecimento/Conhecimento-modelo.xlsx
+++ b/Conhecimento/Conhecimento-modelo.xlsx
@@ -528,7 +528,7 @@
     <t xml:space="preserve">Bolsa térmica fechada até a entrega</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrução IT-05</t>
+    <t xml:space="preserve">Instrução IT-EXP-01</t>
   </si>
   <si>
     <t xml:space="preserve">Gerente</t>
@@ -1023,7 +1023,7 @@
     <t xml:space="preserve">A regulagem do forno precisa estar escrita.</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrução do forno IT-08</t>
+    <t xml:space="preserve">Instrução do forno IT-PRO-02</t>
   </si>
   <si>
     <t xml:space="preserve">Pizzaiolo líder</t>
@@ -2080,11 +2080,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="71090995"/>
-        <c:axId val="93011201"/>
+        <c:axId val="2801349"/>
+        <c:axId val="81402543"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="71090995"/>
+        <c:axId val="2801349"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2116,7 +2116,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93011201"/>
+        <c:crossAx val="81402543"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2124,7 +2124,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="93011201"/>
+        <c:axId val="81402543"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2164,7 +2164,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71090995"/>
+        <c:crossAx val="2801349"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>

--- a/Conhecimento/Conhecimento-modelo.xlsx
+++ b/Conhecimento/Conhecimento-modelo.xlsx
@@ -2080,11 +2080,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="2801349"/>
-        <c:axId val="81402543"/>
+        <c:axId val="29803120"/>
+        <c:axId val="25157057"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2801349"/>
+        <c:axId val="29803120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2116,7 +2116,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81402543"/>
+        <c:crossAx val="25157057"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2124,7 +2124,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81402543"/>
+        <c:axId val="25157057"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2164,7 +2164,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2801349"/>
+        <c:crossAx val="29803120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>

--- a/Conhecimento/Conhecimento-modelo.xlsx
+++ b/Conhecimento/Conhecimento-modelo.xlsx
@@ -1155,7 +1155,7 @@
     <t xml:space="preserve">Indústria de embalagens plásticas</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista da Qualidade, com o gerente de produção</t>
+    <t xml:space="preserve">Analista da Qualidade, com o gerente industrial</t>
   </si>
   <si>
     <t xml:space="preserve">O operador sênior da extrusão se aposenta em dezembro de 2027. O filme D-07 entrou em produção em setembro.</t>
@@ -2080,11 +2080,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="29803120"/>
-        <c:axId val="25157057"/>
+        <c:axId val="37730621"/>
+        <c:axId val="964276"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="29803120"/>
+        <c:axId val="37730621"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2116,7 +2116,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25157057"/>
+        <c:crossAx val="964276"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2124,7 +2124,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25157057"/>
+        <c:axId val="964276"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2164,7 +2164,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29803120"/>
+        <c:crossAx val="37730621"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>

--- a/Conhecimento/Conhecimento-modelo.xlsx
+++ b/Conhecimento/Conhecimento-modelo.xlsx
@@ -252,7 +252,7 @@
     <t xml:space="preserve">Prazo do atendimento</t>
   </si>
   <si>
-    <t xml:space="preserve">O prazo de resposta do produto, na aba Pós-entrega.</t>
+    <t xml:space="preserve">O prazo de solução do produto, na aba Pós-entrega: em quanto tempo o caso é resolvido.</t>
   </si>
   <si>
     <t xml:space="preserve">Dias do atendimento</t>
@@ -291,7 +291,7 @@
     <t xml:space="preserve">Passo 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Aba Pós-entrega: a política de cada produto, com o mínimo da lei ou do contrato, o prazo aceito, o que se faz e o prazo de resposta.</t>
+    <t xml:space="preserve">Aba Pós-entrega: a política de cada produto, com o mínimo da lei ou do contrato, o prazo aceito, o que se faz e o prazo de solução.</t>
   </si>
   <si>
     <t xml:space="preserve">Passo 5</t>
@@ -567,7 +567,7 @@
     <t xml:space="preserve">O que se faz depois da entrega</t>
   </si>
   <si>
-    <t xml:space="preserve">Prazo de resposta (dias)</t>
+    <t xml:space="preserve">Prazo de solução (dias)</t>
   </si>
   <si>
     <t xml:space="preserve">O que se quer evitar no uso</t>
@@ -753,7 +753,7 @@
     <t xml:space="preserve">Fora do prazo, resolvidos ou não</t>
   </si>
   <si>
-    <t xml:space="preserve">Passaram do prazo de resposta.</t>
+    <t xml:space="preserve">Passaram do prazo de solução.</t>
   </si>
   <si>
     <t xml:space="preserve">Resolvidos no prazo</t>
@@ -819,7 +819,7 @@
     <t xml:space="preserve">Os prazos aceitos para reclamar respeitam a lei e os contratos.</t>
   </si>
   <si>
-    <t xml:space="preserve">As reclamações, garantias e assistências são registradas, com prazo de resposta.</t>
+    <t xml:space="preserve">As reclamações, garantias e assistências são registradas, com prazo de solução.</t>
   </si>
   <si>
     <t xml:space="preserve">Cada reclamação resolvida tem a causa registrada.</t>
@@ -861,7 +861,7 @@
     <t xml:space="preserve">Mudança prevista</t>
   </si>
   <si>
-    <t xml:space="preserve">O pizzaiolo líder, há 12 anos na loja, muda de cidade em agosto de 2027.</t>
+    <t xml:space="preserve">O pizzaiolo líder, há seis anos na loja, muda de cidade em agosto de 2027.</t>
   </si>
   <si>
     <t xml:space="preserve">Diagnóstico ISO de 2026: requisito 7.1.6 atendido em parte. As receitas estavam escritas, e a regulagem do forno só o pizzaiolo líder conhecia.</t>
@@ -927,7 +927,7 @@
     <t xml:space="preserve">K-05</t>
   </si>
   <si>
-    <t xml:space="preserve">Uso do sistema de pedidos novo</t>
+    <t xml:space="preserve">Uso do sistema de pedidos, depois da atualização de versão</t>
   </si>
   <si>
     <t xml:space="preserve">Atendimento</t>
@@ -1047,7 +1047,7 @@
     <t xml:space="preserve">O que se faz</t>
   </si>
   <si>
-    <t xml:space="preserve">Resposta (dias)</t>
+    <t xml:space="preserve">Solução (dias)</t>
   </si>
   <si>
     <t xml:space="preserve">O que se quer evitar</t>
@@ -1161,7 +1161,7 @@
     <t xml:space="preserve">O operador sênior da extrusão se aposenta em dezembro de 2027. O filme D-07 entrou em produção em setembro.</t>
   </si>
   <si>
-    <t xml:space="preserve">Análise crítica de julho: as quebras da extrusora 3 mostraram que o desgaste da rosca só era medido pelo técnico do fabricante.</t>
+    <t xml:space="preserve">Análise crítica de 19/08/2027: as quebras da extrusora 3 mostraram que o desgaste da rosca só era medido pelo técnico do fabricante.</t>
   </si>
   <si>
     <t xml:space="preserve">C-01</t>
@@ -1272,7 +1272,7 @@
     <t xml:space="preserve">Na compra de instrumentos, a resolução cabe 10 vezes na tolerância.</t>
   </si>
   <si>
-    <t xml:space="preserve">Procedimento de compras PC-02</t>
+    <t xml:space="preserve">Procedimento PR-SUP-01</t>
   </si>
   <si>
     <t xml:space="preserve">Comprador</t>
@@ -2080,11 +2080,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="37730621"/>
-        <c:axId val="964276"/>
+        <c:axId val="79563831"/>
+        <c:axId val="27826090"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="37730621"/>
+        <c:axId val="79563831"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2116,7 +2116,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="964276"/>
+        <c:crossAx val="27826090"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2124,7 +2124,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="964276"/>
+        <c:axId val="27826090"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2164,7 +2164,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37730621"/>
+        <c:crossAx val="79563831"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -6146,7 +6146,7 @@
       <c r="H7" s="14"/>
       <c r="I7" s="5"/>
       <c r="J7" s="17" t="str">
-        <f aca="false">IF(C7="","",IF(E7="","Falta o prazo mínimo para reclamar",IF(F7="","Falta o prazo aceito",IF(F7&lt;E7,"Prazo aceito menor que o mínimo",IF(G7="","Falta o que se faz",IF(H7="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C7="","",IF(E7="","Falta o prazo mínimo para reclamar",IF(F7="","Falta o prazo aceito",IF(F7&lt;E7,"Prazo aceito menor que o mínimo",IF(G7="","Falta o que se faz",IF(H7="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       <c r="H8" s="14"/>
       <c r="I8" s="5"/>
       <c r="J8" s="17" t="str">
-        <f aca="false">IF(C8="","",IF(E8="","Falta o prazo mínimo para reclamar",IF(F8="","Falta o prazo aceito",IF(F8&lt;E8,"Prazo aceito menor que o mínimo",IF(G8="","Falta o que se faz",IF(H8="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C8="","",IF(E8="","Falta o prazo mínimo para reclamar",IF(F8="","Falta o prazo aceito",IF(F8&lt;E8,"Prazo aceito menor que o mínimo",IF(G8="","Falta o que se faz",IF(H8="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       <c r="H9" s="14"/>
       <c r="I9" s="5"/>
       <c r="J9" s="17" t="str">
-        <f aca="false">IF(C9="","",IF(E9="","Falta o prazo mínimo para reclamar",IF(F9="","Falta o prazo aceito",IF(F9&lt;E9,"Prazo aceito menor que o mínimo",IF(G9="","Falta o que se faz",IF(H9="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C9="","",IF(E9="","Falta o prazo mínimo para reclamar",IF(F9="","Falta o prazo aceito",IF(F9&lt;E9,"Prazo aceito menor que o mínimo",IF(G9="","Falta o que se faz",IF(H9="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       <c r="H10" s="14"/>
       <c r="I10" s="5"/>
       <c r="J10" s="17" t="str">
-        <f aca="false">IF(C10="","",IF(E10="","Falta o prazo mínimo para reclamar",IF(F10="","Falta o prazo aceito",IF(F10&lt;E10,"Prazo aceito menor que o mínimo",IF(G10="","Falta o que se faz",IF(H10="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C10="","",IF(E10="","Falta o prazo mínimo para reclamar",IF(F10="","Falta o prazo aceito",IF(F10&lt;E10,"Prazo aceito menor que o mínimo",IF(G10="","Falta o que se faz",IF(H10="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       <c r="H11" s="14"/>
       <c r="I11" s="5"/>
       <c r="J11" s="17" t="str">
-        <f aca="false">IF(C11="","",IF(E11="","Falta o prazo mínimo para reclamar",IF(F11="","Falta o prazo aceito",IF(F11&lt;E11,"Prazo aceito menor que o mínimo",IF(G11="","Falta o que se faz",IF(H11="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C11="","",IF(E11="","Falta o prazo mínimo para reclamar",IF(F11="","Falta o prazo aceito",IF(F11&lt;E11,"Prazo aceito menor que o mínimo",IF(G11="","Falta o que se faz",IF(H11="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       <c r="H12" s="14"/>
       <c r="I12" s="5"/>
       <c r="J12" s="17" t="str">
-        <f aca="false">IF(C12="","",IF(E12="","Falta o prazo mínimo para reclamar",IF(F12="","Falta o prazo aceito",IF(F12&lt;E12,"Prazo aceito menor que o mínimo",IF(G12="","Falta o que se faz",IF(H12="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C12="","",IF(E12="","Falta o prazo mínimo para reclamar",IF(F12="","Falta o prazo aceito",IF(F12&lt;E12,"Prazo aceito menor que o mínimo",IF(G12="","Falta o que se faz",IF(H12="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       <c r="H13" s="14"/>
       <c r="I13" s="5"/>
       <c r="J13" s="17" t="str">
-        <f aca="false">IF(C13="","",IF(E13="","Falta o prazo mínimo para reclamar",IF(F13="","Falta o prazo aceito",IF(F13&lt;E13,"Prazo aceito menor que o mínimo",IF(G13="","Falta o que se faz",IF(H13="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C13="","",IF(E13="","Falta o prazo mínimo para reclamar",IF(F13="","Falta o prazo aceito",IF(F13&lt;E13,"Prazo aceito menor que o mínimo",IF(G13="","Falta o que se faz",IF(H13="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       <c r="H14" s="14"/>
       <c r="I14" s="5"/>
       <c r="J14" s="17" t="str">
-        <f aca="false">IF(C14="","",IF(E14="","Falta o prazo mínimo para reclamar",IF(F14="","Falta o prazo aceito",IF(F14&lt;E14,"Prazo aceito menor que o mínimo",IF(G14="","Falta o que se faz",IF(H14="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C14="","",IF(E14="","Falta o prazo mínimo para reclamar",IF(F14="","Falta o prazo aceito",IF(F14&lt;E14,"Prazo aceito menor que o mínimo",IF(G14="","Falta o que se faz",IF(H14="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       <c r="H15" s="14"/>
       <c r="I15" s="5"/>
       <c r="J15" s="17" t="str">
-        <f aca="false">IF(C15="","",IF(E15="","Falta o prazo mínimo para reclamar",IF(F15="","Falta o prazo aceito",IF(F15&lt;E15,"Prazo aceito menor que o mínimo",IF(G15="","Falta o que se faz",IF(H15="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C15="","",IF(E15="","Falta o prazo mínimo para reclamar",IF(F15="","Falta o prazo aceito",IF(F15&lt;E15,"Prazo aceito menor que o mínimo",IF(G15="","Falta o que se faz",IF(H15="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       <c r="H16" s="14"/>
       <c r="I16" s="5"/>
       <c r="J16" s="17" t="str">
-        <f aca="false">IF(C16="","",IF(E16="","Falta o prazo mínimo para reclamar",IF(F16="","Falta o prazo aceito",IF(F16&lt;E16,"Prazo aceito menor que o mínimo",IF(G16="","Falta o que se faz",IF(H16="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C16="","",IF(E16="","Falta o prazo mínimo para reclamar",IF(F16="","Falta o prazo aceito",IF(F16&lt;E16,"Prazo aceito menor que o mínimo",IF(G16="","Falta o que se faz",IF(H16="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       <c r="H17" s="14"/>
       <c r="I17" s="5"/>
       <c r="J17" s="17" t="str">
-        <f aca="false">IF(C17="","",IF(E17="","Falta o prazo mínimo para reclamar",IF(F17="","Falta o prazo aceito",IF(F17&lt;E17,"Prazo aceito menor que o mínimo",IF(G17="","Falta o que se faz",IF(H17="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C17="","",IF(E17="","Falta o prazo mínimo para reclamar",IF(F17="","Falta o prazo aceito",IF(F17&lt;E17,"Prazo aceito menor que o mínimo",IF(G17="","Falta o que se faz",IF(H17="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       <c r="H18" s="14"/>
       <c r="I18" s="5"/>
       <c r="J18" s="17" t="str">
-        <f aca="false">IF(C18="","",IF(E18="","Falta o prazo mínimo para reclamar",IF(F18="","Falta o prazo aceito",IF(F18&lt;E18,"Prazo aceito menor que o mínimo",IF(G18="","Falta o que se faz",IF(H18="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C18="","",IF(E18="","Falta o prazo mínimo para reclamar",IF(F18="","Falta o prazo aceito",IF(F18&lt;E18,"Prazo aceito menor que o mínimo",IF(G18="","Falta o que se faz",IF(H18="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       <c r="H19" s="14"/>
       <c r="I19" s="5"/>
       <c r="J19" s="17" t="str">
-        <f aca="false">IF(C19="","",IF(E19="","Falta o prazo mínimo para reclamar",IF(F19="","Falta o prazo aceito",IF(F19&lt;E19,"Prazo aceito menor que o mínimo",IF(G19="","Falta o que se faz",IF(H19="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C19="","",IF(E19="","Falta o prazo mínimo para reclamar",IF(F19="","Falta o prazo aceito",IF(F19&lt;E19,"Prazo aceito menor que o mínimo",IF(G19="","Falta o que se faz",IF(H19="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       <c r="H20" s="14"/>
       <c r="I20" s="5"/>
       <c r="J20" s="17" t="str">
-        <f aca="false">IF(C20="","",IF(E20="","Falta o prazo mínimo para reclamar",IF(F20="","Falta o prazo aceito",IF(F20&lt;E20,"Prazo aceito menor que o mínimo",IF(G20="","Falta o que se faz",IF(H20="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C20="","",IF(E20="","Falta o prazo mínimo para reclamar",IF(F20="","Falta o prazo aceito",IF(F20&lt;E20,"Prazo aceito menor que o mínimo",IF(G20="","Falta o que se faz",IF(H20="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6370,7 +6370,7 @@
       <c r="H21" s="14"/>
       <c r="I21" s="5"/>
       <c r="J21" s="17" t="str">
-        <f aca="false">IF(C21="","",IF(E21="","Falta o prazo mínimo para reclamar",IF(F21="","Falta o prazo aceito",IF(F21&lt;E21,"Prazo aceito menor que o mínimo",IF(G21="","Falta o que se faz",IF(H21="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C21="","",IF(E21="","Falta o prazo mínimo para reclamar",IF(F21="","Falta o prazo aceito",IF(F21&lt;E21,"Prazo aceito menor que o mínimo",IF(G21="","Falta o que se faz",IF(H21="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       <c r="H22" s="14"/>
       <c r="I22" s="5"/>
       <c r="J22" s="17" t="str">
-        <f aca="false">IF(C22="","",IF(E22="","Falta o prazo mínimo para reclamar",IF(F22="","Falta o prazo aceito",IF(F22&lt;E22,"Prazo aceito menor que o mínimo",IF(G22="","Falta o que se faz",IF(H22="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C22="","",IF(E22="","Falta o prazo mínimo para reclamar",IF(F22="","Falta o prazo aceito",IF(F22&lt;E22,"Prazo aceito menor que o mínimo",IF(G22="","Falta o que se faz",IF(H22="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       <c r="H23" s="14"/>
       <c r="I23" s="5"/>
       <c r="J23" s="17" t="str">
-        <f aca="false">IF(C23="","",IF(E23="","Falta o prazo mínimo para reclamar",IF(F23="","Falta o prazo aceito",IF(F23&lt;E23,"Prazo aceito menor que o mínimo",IF(G23="","Falta o que se faz",IF(H23="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C23="","",IF(E23="","Falta o prazo mínimo para reclamar",IF(F23="","Falta o prazo aceito",IF(F23&lt;E23,"Prazo aceito menor que o mínimo",IF(G23="","Falta o que se faz",IF(H23="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       <c r="H24" s="14"/>
       <c r="I24" s="5"/>
       <c r="J24" s="17" t="str">
-        <f aca="false">IF(C24="","",IF(E24="","Falta o prazo mínimo para reclamar",IF(F24="","Falta o prazo aceito",IF(F24&lt;E24,"Prazo aceito menor que o mínimo",IF(G24="","Falta o que se faz",IF(H24="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C24="","",IF(E24="","Falta o prazo mínimo para reclamar",IF(F24="","Falta o prazo aceito",IF(F24&lt;E24,"Prazo aceito menor que o mínimo",IF(G24="","Falta o que se faz",IF(H24="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       <c r="H25" s="14"/>
       <c r="I25" s="5"/>
       <c r="J25" s="17" t="str">
-        <f aca="false">IF(C25="","",IF(E25="","Falta o prazo mínimo para reclamar",IF(F25="","Falta o prazo aceito",IF(F25&lt;E25,"Prazo aceito menor que o mínimo",IF(G25="","Falta o que se faz",IF(H25="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C25="","",IF(E25="","Falta o prazo mínimo para reclamar",IF(F25="","Falta o prazo aceito",IF(F25&lt;E25,"Prazo aceito menor que o mínimo",IF(G25="","Falta o que se faz",IF(H25="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       <c r="H26" s="14"/>
       <c r="I26" s="5"/>
       <c r="J26" s="17" t="str">
-        <f aca="false">IF(C26="","",IF(E26="","Falta o prazo mínimo para reclamar",IF(F26="","Falta o prazo aceito",IF(F26&lt;E26,"Prazo aceito menor que o mínimo",IF(G26="","Falta o que se faz",IF(H26="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(C26="","",IF(E26="","Falta o prazo mínimo para reclamar",IF(F26="","Falta o prazo aceito",IF(F26&lt;E26,"Prazo aceito menor que o mínimo",IF(G26="","Falta o que se faz",IF(H26="","Falta o prazo de solução","OK"))))))</f>
         <v/>
       </c>
     </row>
@@ -11013,7 +11013,7 @@
       <c r="O31" s="40"/>
       <c r="P31" s="40"/>
       <c r="Q31" s="17" t="str">
-        <f aca="false">IF(B31="","",IF(F31="","Falta o prazo mínimo para reclamar",IF(G31="","Falta o prazo aceito",IF(G31&lt;F31,"Prazo aceito menor que o mínimo",IF(H31="","Falta o que se faz",IF(L31="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(B31="","",IF(F31="","Falta o prazo mínimo para reclamar",IF(G31="","Falta o prazo aceito",IF(G31&lt;F31,"Prazo aceito menor que o mínimo",IF(H31="","Falta o que se faz",IF(L31="","Falta o prazo de solução","OK"))))))</f>
         <v>Prazo aceito menor que o mínimo</v>
       </c>
     </row>
@@ -11046,7 +11046,7 @@
       <c r="O32" s="40"/>
       <c r="P32" s="40"/>
       <c r="Q32" s="17" t="str">
-        <f aca="false">IF(B32="","",IF(F32="","Falta o prazo mínimo para reclamar",IF(G32="","Falta o prazo aceito",IF(G32&lt;F32,"Prazo aceito menor que o mínimo",IF(H32="","Falta o que se faz",IF(L32="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(B32="","",IF(F32="","Falta o prazo mínimo para reclamar",IF(G32="","Falta o prazo aceito",IF(G32&lt;F32,"Prazo aceito menor que o mínimo",IF(H32="","Falta o que se faz",IF(L32="","Falta o prazo de solução","OK"))))))</f>
         <v>OK</v>
       </c>
     </row>
@@ -11081,7 +11081,7 @@
       <c r="O33" s="40"/>
       <c r="P33" s="40"/>
       <c r="Q33" s="17" t="str">
-        <f aca="false">IF(B33="","",IF(F33="","Falta o prazo mínimo para reclamar",IF(G33="","Falta o prazo aceito",IF(G33&lt;F33,"Prazo aceito menor que o mínimo",IF(H33="","Falta o que se faz",IF(L33="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(B33="","",IF(F33="","Falta o prazo mínimo para reclamar",IF(G33="","Falta o prazo aceito",IF(G33&lt;F33,"Prazo aceito menor que o mínimo",IF(H33="","Falta o que se faz",IF(L33="","Falta o prazo de solução","OK"))))))</f>
         <v>OK</v>
       </c>
     </row>
@@ -12789,7 +12789,7 @@
       <c r="O32" s="40"/>
       <c r="P32" s="40"/>
       <c r="Q32" s="17" t="str">
-        <f aca="false">IF(B32="","",IF(F32="","Falta o prazo mínimo para reclamar",IF(G32="","Falta o prazo aceito",IF(G32&lt;F32,"Prazo aceito menor que o mínimo",IF(H32="","Falta o que se faz",IF(L32="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(B32="","",IF(F32="","Falta o prazo mínimo para reclamar",IF(G32="","Falta o prazo aceito",IF(G32&lt;F32,"Prazo aceito menor que o mínimo",IF(H32="","Falta o que se faz",IF(L32="","Falta o prazo de solução","OK"))))))</f>
         <v>OK</v>
       </c>
     </row>
@@ -12822,7 +12822,7 @@
       <c r="O33" s="40"/>
       <c r="P33" s="40"/>
       <c r="Q33" s="17" t="str">
-        <f aca="false">IF(B33="","",IF(F33="","Falta o prazo mínimo para reclamar",IF(G33="","Falta o prazo aceito",IF(G33&lt;F33,"Prazo aceito menor que o mínimo",IF(H33="","Falta o que se faz",IF(L33="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(B33="","",IF(F33="","Falta o prazo mínimo para reclamar",IF(G33="","Falta o prazo aceito",IF(G33&lt;F33,"Prazo aceito menor que o mínimo",IF(H33="","Falta o que se faz",IF(L33="","Falta o prazo de solução","OK"))))))</f>
         <v>OK</v>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       <c r="O34" s="40"/>
       <c r="P34" s="40"/>
       <c r="Q34" s="17" t="str">
-        <f aca="false">IF(B34="","",IF(F34="","Falta o prazo mínimo para reclamar",IF(G34="","Falta o prazo aceito",IF(G34&lt;F34,"Prazo aceito menor que o mínimo",IF(H34="","Falta o que se faz",IF(L34="","Falta o prazo de resposta","OK"))))))</f>
+        <f aca="false">IF(B34="","",IF(F34="","Falta o prazo mínimo para reclamar",IF(G34="","Falta o prazo aceito",IF(G34&lt;F34,"Prazo aceito menor que o mínimo",IF(H34="","Falta o que se faz",IF(L34="","Falta o prazo de solução","OK"))))))</f>
         <v>Prazo aceito menor que o mínimo</v>
       </c>
     </row>

--- a/Conhecimento/Conhecimento-modelo.xlsx
+++ b/Conhecimento/Conhecimento-modelo.xlsx
@@ -1341,7 +1341,7 @@
     <t xml:space="preserve">12 meses em estoque, de 15 a 30 °C</t>
   </si>
   <si>
-    <t xml:space="preserve">Laudo da reclamação técnica, visita técnica quando pedida, reposição do lote.</t>
+    <t xml:space="preserve">Laudo técnico do defeito, visita técnica quando pedida, reposição do lote.</t>
   </si>
   <si>
     <t xml:space="preserve">Embalagem rompendo no freezer do consumidor.</t>
@@ -1353,13 +1353,13 @@
     <t xml:space="preserve">12 meses em estoque</t>
   </si>
   <si>
-    <t xml:space="preserve">Laudo da reclamação técnica e reposição do lote.</t>
+    <t xml:space="preserve">Laudo técnico do defeito e reposição do lote.</t>
   </si>
   <si>
     <t xml:space="preserve">Filme impresso</t>
   </si>
   <si>
-    <t xml:space="preserve">Laudo da reclamação técnica, prova de cor e reposição do lote.</t>
+    <t xml:space="preserve">Laudo técnico do defeito, prova de cor e reposição do lote.</t>
   </si>
   <si>
     <t xml:space="preserve">Cor diferente da marca do cliente na gôndola.</t>
@@ -2080,11 +2080,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="79563831"/>
-        <c:axId val="27826090"/>
+        <c:axId val="96102026"/>
+        <c:axId val="75625840"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="79563831"/>
+        <c:axId val="96102026"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2116,7 +2116,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27826090"/>
+        <c:crossAx val="75625840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2124,7 +2124,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="27826090"/>
+        <c:axId val="75625840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2164,7 +2164,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79563831"/>
+        <c:crossAx val="96102026"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -12678,7 +12678,7 @@
         <v>46645</v>
       </c>
       <c r="E28" s="39" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="F28" s="40" t="s">
         <v>385</v>
